--- a/data/output/evaluasi_92.xlsx
+++ b/data/output/evaluasi_92.xlsx
@@ -8,7 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="9200" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="9271" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="9201" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="9271" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="9203" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="9205" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="9202" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="9204" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +481,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.257010263506596</v>
+        <v>5.25701026350695</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -485,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -500,20 +505,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.253073538258445</v>
+        <v>-7.275128477944537</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_pi_q2-25</t>
+          <t>adhb_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -532,16 +537,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.090358535681339</v>
+        <v>-5.084456662070581</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q2-25 vs y-on-y_pmtb_q2-25.1</t>
+          <t>adhb_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -556,20 +561,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.3607875005733722</v>
+        <v>-9.401754919010608</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pdrb_q2-25 vs implisit_q-to-q_pdrb_q2-25.1</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -584,20 +589,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.3191128815034591</v>
+        <v>5.140557481265696</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25 vs implisit_q-to-q_pkrt_q1-25.1</t>
+          <t>adhk_pklnprt_q2-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -612,20 +617,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.1099890690213117</v>
+        <v>5.199140274817115</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q2-25 vs implisit_q-to-q_pkrt_q2-25.1</t>
+          <t>adhk_pklnprt_q3-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -640,20 +645,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.284959620688614</v>
+        <v>0.2917804180736343</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+          <t>q-to-q_pdrb_q2-25 vs q-to-q_pdrb_q2-25.1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
         </is>
       </c>
     </row>
@@ -668,20 +673,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-6.323988951189392</v>
+        <v>-5.363848991899977</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25 vs implisit_q-to-q_pmtb_q1-25.1</t>
+          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -696,20 +701,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.847678816602217</v>
+        <v>-27.00358144962629</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -728,16 +733,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.006290886014836515</v>
+        <v>6.703933617746991</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q2-25 vs implisit_y-on-y_pkrt_q2-25.1</t>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -752,20 +757,888 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5.733604611387036</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>92</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>5.166929959694723</v>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D13" t="n">
+        <v>5.996378972858707</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q2-25 vs q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>92</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.414625157603819</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25 vs q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>92</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4.349745479469961</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>92</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5.544566361646585</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q1-25 vs y-on-y_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>92</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5.004644036239491</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>92</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>8.63950694454574</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q2-25 vs y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>92</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.951646594395997</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>92</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4.467342849568298</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>92</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5.544566361646585</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q1-25 vs c-to-c_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>92</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4.302995199262503</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q2-25 vs c-to-c_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>92</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>9.017680984599744</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q2-25 vs c-to-c_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>92</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>6.616116864343089</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25 vs c-to-c_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>92</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>4.467342849568298</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>92</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>4.897166645527435</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>92</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-1.415521667813465</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q1-25 vs implisit_q-to-q_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>92</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.2976097287843927</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25 vs implisit_q-to-q_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>92</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3.335445694392445</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q2-25 vs implisit_q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>92</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.9787049308325978</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25 vs implisit_q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>92</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>4.284959620688614</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>92</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3.66153397779982</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q2-25 vs implisit_q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>92</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>-6.355971296352182</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q1-25 vs implisit_q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>92</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2.781911201470538</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>92</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3.828071929470332</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25 vs implisit_q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>92</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.02489816719101643</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q2-25 vs implisit_y-on-y_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>92</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.1198116832101928</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25 vs implisit_y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>92</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>5.428008211167688</v>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>implisit_y-on-y_pklnprt_q2-25 vs implisit_y-on-y_pklnprt_q2-25.1</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>92</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4.479457808794047</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25 vs implisit_y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>92</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>-4.022235407014515</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q1-25 vs implisit_y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>92</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.2197802880555809</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25 vs implisit_y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>92</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.7781434445410927</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>92</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Papua Barat Daya</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>-4.318996519866988</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25 vs implisit_y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -780,7 +1653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -817,6 +1690,528 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>29724.90472967958</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>adhb_pi_q2-25_ril vs adhb_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.014859900447351</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-4.329107185757534</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-10.87017062021937</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.603885492302562</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3399999999999944</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.469390973257894</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.0357007968508</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.732023807312643</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-9.490012929579784</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-12.17897959822855</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.307028107896956</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-9.199856184951061</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.286580028879498</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.050000000000015</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.740000000000005</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.330388083293358</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>9271</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,20 +2221,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-157146.40183966</v>
+        <v>1.118600726314325</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>implisit_y-on-y_pmtb_q2-25_ril vs implisit_y-on-y_pmtb_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -858,16 +2253,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>420357.598860591</v>
+        <v>6.174199356635063</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -886,16 +2281,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08174863221184876</v>
+        <v>-21.04247448565998</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -910,20 +2305,2080 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.529905951837338</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.037252269270203</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.648724995014617</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.491808248939289</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1722651200896266</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.03424708341054333</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5.737264999507063</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.391195446506345</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25_prov vs implisit_y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.952869491932606</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7.423013679543888</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
+      <c r="D2" t="n">
+        <v>25.01978138513372</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.849641035315281</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.027178203343007</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
       <c r="D5" t="n">
-        <v>5.730502702217477</v>
+        <v>6.130147070841052</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>26.98830307068442</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.608228001107029</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>26.26136049621632</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7443639168565018</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.09994245558154671</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.20779049182592</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.7182809405161663</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8552749008161084</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4747803172422414</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5.483014824135097</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.96749988148582</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6.51742603715402</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.905610124454758</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>8.148762260564762</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6.571444667939493</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.476855177461882</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-4.521218169716231</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>17.19775812888759</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.98152660811507</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.213613703018593</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.188540957641054</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.6680395762252764</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-6.797018886791675</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.44600839170292</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8.030697333726218</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.1394258797847882</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10.87400529084206</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1938698144602272</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.8402850683573154</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25_prov vs implisit_y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5.246659883464044</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-4.238946634870105</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.058514095812246</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.107354316570778</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.710817522069732</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.249666098267896</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.710623947944007</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.324859508176853</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.583842715157286</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9.684850380147903</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3150312044321945</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4.623884984966021</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.494754669378521</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7.328671045231129</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.299926309538217</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.685954726081334</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-7.273664226764747</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.38279157762703</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.058620253591682</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.585728436925123</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.4629906686248046</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1207643441592435</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.298329739649906</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7.616901352279928</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.403336819582888</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_92.xlsx
+++ b/data/output/evaluasi_92.xlsx
@@ -658,7 +658,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
